--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0146.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0146.xlsx
@@ -3629,7 +3629,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Ta sẽ giúp ngươi tìm mối liên hệ giữa âm nhạc và lũ Daemon đó. Nhưng đổi lại, ngươi phải đưa mấy trang này cho ta giữ.</t>
+          <t>Tao sẽ giúp mày tìm mối liên hệ giữa âm nhạc và lũ Daemon đó. Nhưng đổi lại, mày phải đưa mấy trang này cho tao giữ.</t>
         </is>
       </c>
     </row>
@@ -7464,7 +7464,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Vậy thì, chúng ta hãy bắt đầu từ đầu nhé. Ta có một người bạn là chuyên gia giải mã âm nhạc. Ta tin là cậu đã gặp cô ấy rồi...</t>
+          <t>Vậy thì, chúng ta hãy bắt đầu từ đầu nhé. Tao có một người bạn là chuyên gia giải mã âm nhạc. Tao tin là cậu đã gặp cô ấy rồi...</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Ta không rõ hắn thực sự là ai... Nhưng đoán chừng hắn có thể là Cộng Hưởng Giả đang hợp tác với Order.</t>
+          <t>Ta không rõ hắn thực sự là ai... Nhưng đoán chừng hắn có thể là Resonator đang hợp tác với Order.</t>
         </is>
       </c>
     </row>
@@ -9804,7 +9804,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>...Chỉ nghĩ đến việc đối đầu với họ thôi đã khiến ta muốn viết một bản ballad rồi! Đặt tên gì nhỉ? Dùng nhạc cụ nào cho hợp...</t>
+          <t>...Chỉ nghĩ đến việc đối đầu với họ thôi đã khiến tao muốn viết một bản ballad rồi! Đặt tên gì nhỉ? Dùng nhạc cụ nào cho hợp...</t>
         </is>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Nếu tìm được &lt;te href=800012&gt;Melody&lt;/te&gt; liên quan đến Hội Thi Sĩ, tôi có thể làm sáng tỏ quá khứ...</t>
+          <t>Nếu tìm được &lt;te href=800012&gt;Giai Điệu&lt;/te&gt; liên quan đến Hội Thi Sĩ, tôi có thể làm sáng tỏ quá khứ...</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Tadaa! Chào mừng đến với &lt;te href=800010&gt;Requiem Paradise&lt;/te&gt;!</t>
+          <t>Tadaa! Chào mừng đến với &lt;te href=800010&gt;Thiên Đường Khúc Bi Ca&lt;/te&gt;!</t>
         </is>
       </c>
     </row>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Thế là ta đứng dưới gốc cây cầu nguyện cho một quả táo rơi trúng đầu.</t>
+          <t>Thế là tao đứng dưới gốc cây cầu nguyện cho một quả táo rơi trúng đầu.</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Ta đã biết đây sẽ là số phận của chúng ta.</t>
+          <t>Tao đã biết đây sẽ là số phận của chúng ta.</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>Chúng ta không phải là những nhà thám hiểm hay những Cộng Hưởng Giả hùng mạnh. Thậm chí còn chẳng có thời gian lẫn khả năng để xác định tấm bản đồ đá đó thật hay giả.</t>
+          <t>Chúng ta không phải là những nhà thám hiểm hay những Resonator hùng mạnh. Thậm chí còn chẳng có thời gian lẫn khả năng để xác định tấm bản đồ đá đó thật hay giả.</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Đây... là một bài thơ ta chưa từng thấy. Nó khác hẳn những gì người ta vẫn viết trước đây.</t>
+          <t>Đây... là một bài thơ tao chưa từng thấy. Nó khác hẳn những gì người ta vẫn viết trước đây.</t>
         </is>
       </c>
     </row>
@@ -16109,7 +16109,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>"Ta là chim ưng đêm với đôi cánh rực lửa, vút bay về phía &lt;te href=800011&gt;Celestial Steed&lt;/te&gt;, ta ngợi ca và chiêm ngưỡng chân dung thực sự của Người."</t>
+          <t>"Ta là chim ưng đêm với đôi cánh rực lửa, vút bay về phía &lt;te href=800011&gt;Thiên Mã&lt;/te&gt;, ta ngợi ca và chiêm ngưỡng chân dung thực sự của Người."</t>
         </is>
       </c>
     </row>
